--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.94013</v>
+        <v>17.23098</v>
       </c>
       <c r="D2" t="n">
-        <v>16.7459</v>
+        <v>16.77569</v>
       </c>
       <c r="E2" t="n">
-        <v>16.89575</v>
+        <v>16.77689</v>
       </c>
       <c r="F2" t="n">
-        <v>43.82379</v>
+        <v>42.26356</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0516</v>
+        <v>0.05098</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85975</v>
+        <v>1.85043</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.78876</v>
+        <v>16.86613</v>
       </c>
       <c r="D3" t="n">
-        <v>17.19007</v>
+        <v>16.6716</v>
       </c>
       <c r="E3" t="n">
-        <v>16.68327</v>
+        <v>16.73395</v>
       </c>
       <c r="F3" t="n">
-        <v>42.49076</v>
+        <v>43.66977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0513</v>
+        <v>0.05125</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87602</v>
+        <v>1.8925</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.62826</v>
+        <v>17.15864</v>
       </c>
       <c r="D4" t="n">
-        <v>16.51057</v>
+        <v>16.53494</v>
       </c>
       <c r="E4" t="n">
-        <v>16.62911</v>
+        <v>16.5873</v>
       </c>
       <c r="F4" t="n">
-        <v>43.77534</v>
+        <v>43.23271</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05161</v>
+        <v>0.04958</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8567</v>
+        <v>1.85785</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.77786</v>
+        <v>16.65809</v>
       </c>
       <c r="D5" t="n">
-        <v>16.43179</v>
+        <v>16.59741</v>
       </c>
       <c r="E5" t="n">
-        <v>16.92815</v>
+        <v>16.64034</v>
       </c>
       <c r="F5" t="n">
-        <v>43.24134</v>
+        <v>43.25151</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05156</v>
+        <v>0.05096</v>
       </c>
       <c r="H5" t="n">
-        <v>1.79766</v>
+        <v>1.89196</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.98212</v>
+        <v>17.11768</v>
       </c>
       <c r="D7" t="n">
-        <v>16.94123</v>
+        <v>16.58479</v>
       </c>
       <c r="E7" t="n">
-        <v>16.60098</v>
+        <v>16.9005</v>
       </c>
       <c r="F7" t="n">
-        <v>43.24452</v>
+        <v>42.57707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05257</v>
+        <v>0.05098</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84908</v>
+        <v>1.8326</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.95336</v>
+        <v>16.98869</v>
       </c>
       <c r="D8" t="n">
-        <v>16.76953</v>
+        <v>16.89593</v>
       </c>
       <c r="E8" t="n">
-        <v>16.86064</v>
+        <v>16.92303</v>
       </c>
       <c r="F8" t="n">
-        <v>43.2512</v>
+        <v>42.6532</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05018</v>
+        <v>0.051</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82795</v>
+        <v>1.84031</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.90823</v>
+        <v>17.22214</v>
       </c>
       <c r="D9" t="n">
-        <v>17.0816</v>
+        <v>16.81234</v>
       </c>
       <c r="E9" t="n">
-        <v>16.86069</v>
+        <v>17.01083</v>
       </c>
       <c r="F9" t="n">
-        <v>42.59024</v>
+        <v>42.66169</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05041</v>
+        <v>0.05052</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8501</v>
+        <v>1.86599</v>
       </c>
     </row>
     <row r="10">
@@ -647,22 +647,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.92879</v>
+        <v>17.33895</v>
       </c>
       <c r="D10" t="n">
-        <v>17.16727</v>
+        <v>16.99664</v>
       </c>
       <c r="E10" t="n">
-        <v>16.8565</v>
+        <v>17.01088</v>
       </c>
       <c r="F10" t="n">
-        <v>42.98981</v>
+        <v>43.18223</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05071</v>
+        <v>0.05113</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82244</v>
+        <v>1.84236</v>
       </c>
     </row>
     <row r="11">
@@ -704,19 +704,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.84155</v>
+        <v>16.96633</v>
       </c>
       <c r="D12" t="n">
-        <v>16.07916</v>
+        <v>16.46506</v>
       </c>
       <c r="E12" t="n">
-        <v>16.8588</v>
+        <v>16.54366</v>
       </c>
       <c r="F12" t="n">
-        <v>22.15629</v>
+        <v>22.17975</v>
       </c>
       <c r="G12" t="n">
-        <v>34.305</v>
+        <v>34.76872</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +726,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.06209</v>
+        <v>17.0804</v>
       </c>
       <c r="D13" t="n">
-        <v>16.03497</v>
+        <v>16.01508</v>
       </c>
       <c r="E13" t="n">
-        <v>16.50828</v>
+        <v>16.18188</v>
       </c>
       <c r="F13" t="n">
-        <v>22.0357</v>
+        <v>22.15208</v>
       </c>
       <c r="G13" t="n">
-        <v>34.55105</v>
+        <v>34.48845</v>
       </c>
     </row>
     <row r="14">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.72257</v>
+        <v>16.61014</v>
       </c>
       <c r="D14" t="n">
-        <v>16.0248</v>
+        <v>16.23139</v>
       </c>
       <c r="E14" t="n">
-        <v>16.26553</v>
+        <v>16.6059</v>
       </c>
       <c r="F14" t="n">
-        <v>22.13054</v>
+        <v>22.01844</v>
       </c>
       <c r="G14" t="n">
-        <v>35.59185</v>
+        <v>34.53024</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.12651</v>
+        <v>17.40735</v>
       </c>
       <c r="D15" t="n">
-        <v>16.35237</v>
+        <v>16.11027</v>
       </c>
       <c r="E15" t="n">
-        <v>16.37104</v>
+        <v>16.84828</v>
       </c>
       <c r="F15" t="n">
-        <v>21.97573</v>
+        <v>21.85796</v>
       </c>
       <c r="G15" t="n">
-        <v>34.351</v>
+        <v>34.4607</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.71337</v>
+        <v>16.87679</v>
       </c>
       <c r="D16" t="n">
-        <v>15.7248</v>
+        <v>16.19741</v>
       </c>
       <c r="E16" t="n">
-        <v>16.60537</v>
+        <v>16.71792</v>
       </c>
       <c r="F16" t="n">
-        <v>22.01828</v>
+        <v>21.80617</v>
       </c>
       <c r="G16" t="n">
-        <v>35.16095</v>
+        <v>34.57362</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.10758</v>
+        <v>16.86681</v>
       </c>
       <c r="D17" t="n">
-        <v>16.4931</v>
+        <v>16.2571</v>
       </c>
       <c r="E17" t="n">
-        <v>16.6943</v>
+        <v>16.68516</v>
       </c>
       <c r="F17" t="n">
-        <v>21.99007</v>
+        <v>22.24334</v>
       </c>
       <c r="G17" t="n">
-        <v>34.2471</v>
+        <v>34.51985</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.45809</v>
+        <v>17.00448</v>
       </c>
       <c r="D18" t="n">
-        <v>16.19676</v>
+        <v>16.29064</v>
       </c>
       <c r="E18" t="n">
-        <v>16.54539</v>
+        <v>16.85772</v>
       </c>
       <c r="F18" t="n">
-        <v>22.39358</v>
+        <v>22.38605</v>
       </c>
       <c r="G18" t="n">
-        <v>34.69111</v>
+        <v>34.57778</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.79991</v>
+        <v>16.70782</v>
       </c>
       <c r="D19" t="n">
-        <v>16.1157</v>
+        <v>16.1511</v>
       </c>
       <c r="E19" t="n">
-        <v>16.4205</v>
+        <v>16.61874</v>
       </c>
       <c r="F19" t="n">
-        <v>22.32538</v>
+        <v>22.45685</v>
       </c>
       <c r="G19" t="n">
-        <v>34.50234</v>
+        <v>34.56539</v>
       </c>
     </row>
     <row r="20">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.82039</v>
+        <v>16.92074</v>
       </c>
       <c r="D20" t="n">
-        <v>16.06476</v>
+        <v>16.54891</v>
       </c>
       <c r="E20" t="n">
-        <v>16.30906</v>
+        <v>16.64109</v>
       </c>
       <c r="F20" t="n">
-        <v>21.55031</v>
+        <v>21.89987</v>
       </c>
       <c r="G20" t="n">
-        <v>34.71328</v>
+        <v>35.16522</v>
       </c>
     </row>
   </sheetData>
